--- a/example_OP-13.xlsx
+++ b/example_OP-13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Учеба\Политех\4 курс\Проектирование ЧМИ\Лаба 3\Lab 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01967BF8-A927-4122-B4B7-0209D6C00466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A767F2DF-0E91-4FE5-861F-C448327B4C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>Утверждена постановлением Госкомстата</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>Наименование</t>
-  </si>
-  <si>
-    <t>код</t>
   </si>
   <si>
     <t>Итого</t>
@@ -317,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -359,7 +356,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -381,88 +377,88 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -949,18 +945,18 @@
       <c r="AN4"/>
       <c r="AO4"/>
       <c r="AP4"/>
-      <c r="AQ4" s="37" t="s">
+      <c r="AQ4" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="AR4" s="37"/>
-      <c r="AS4" s="37"/>
-      <c r="AT4" s="37"/>
-      <c r="AU4" s="37"/>
-      <c r="AV4" s="37"/>
-      <c r="AW4" s="37"/>
-      <c r="AX4" s="37"/>
-      <c r="AY4" s="37"/>
-      <c r="AZ4" s="37"/>
+      <c r="AR4" s="39"/>
+      <c r="AS4" s="39"/>
+      <c r="AT4" s="39"/>
+      <c r="AU4" s="39"/>
+      <c r="AV4" s="39"/>
+      <c r="AW4" s="39"/>
+      <c r="AX4" s="39"/>
+      <c r="AY4" s="39"/>
+      <c r="AZ4" s="39"/>
     </row>
     <row r="5" spans="1:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="AH5" s="4"/>
@@ -973,179 +969,179 @@
         <v>3</v>
       </c>
       <c r="AP5" s="5"/>
-      <c r="AQ5" s="39" t="s">
+      <c r="AQ5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="AR5" s="39"/>
-      <c r="AS5" s="39"/>
-      <c r="AT5" s="39"/>
-      <c r="AU5" s="39"/>
-      <c r="AV5" s="39"/>
-      <c r="AW5" s="39"/>
-      <c r="AX5" s="39"/>
-      <c r="AY5" s="39"/>
-      <c r="AZ5" s="39"/>
+      <c r="AR5" s="40"/>
+      <c r="AS5" s="40"/>
+      <c r="AT5" s="40"/>
+      <c r="AU5" s="40"/>
+      <c r="AV5" s="40"/>
+      <c r="AW5" s="40"/>
+      <c r="AX5" s="40"/>
+      <c r="AY5" s="40"/>
+      <c r="AZ5" s="40"/>
     </row>
     <row r="6" spans="1:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="51"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51"/>
-      <c r="Z6" s="51"/>
-      <c r="AA6" s="51"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="51"/>
-      <c r="AD6" s="51"/>
-      <c r="AE6" s="51"/>
-      <c r="AF6" s="51"/>
-      <c r="AG6" s="51"/>
-      <c r="AH6" s="51"/>
-      <c r="AI6" s="51"/>
-      <c r="AJ6" s="51"/>
+      <c r="A6" s="48"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="48"/>
+      <c r="X6" s="48"/>
+      <c r="Y6" s="48"/>
+      <c r="Z6" s="48"/>
+      <c r="AA6" s="48"/>
+      <c r="AB6" s="48"/>
+      <c r="AC6" s="48"/>
+      <c r="AD6" s="48"/>
+      <c r="AE6" s="48"/>
+      <c r="AF6" s="48"/>
+      <c r="AG6" s="48"/>
+      <c r="AH6" s="48"/>
+      <c r="AI6" s="48"/>
+      <c r="AJ6" s="48"/>
       <c r="AN6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="AQ6" s="39"/>
-      <c r="AR6" s="39"/>
-      <c r="AS6" s="39"/>
-      <c r="AT6" s="39"/>
-      <c r="AU6" s="39"/>
-      <c r="AV6" s="39"/>
-      <c r="AW6" s="39"/>
-      <c r="AX6" s="39"/>
-      <c r="AY6" s="39"/>
-      <c r="AZ6" s="39"/>
+      <c r="AQ6" s="40"/>
+      <c r="AR6" s="40"/>
+      <c r="AS6" s="40"/>
+      <c r="AT6" s="40"/>
+      <c r="AU6" s="40"/>
+      <c r="AV6" s="40"/>
+      <c r="AW6" s="40"/>
+      <c r="AX6" s="40"/>
+      <c r="AY6" s="40"/>
+      <c r="AZ6" s="40"/>
     </row>
     <row r="7" spans="1:52" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="20"/>
-      <c r="AD7" s="20"/>
-      <c r="AE7" s="20"/>
-      <c r="AF7" s="20"/>
-      <c r="AG7" s="20"/>
-      <c r="AH7" s="20"/>
-      <c r="AI7" s="20"/>
-      <c r="AJ7" s="20"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="19"/>
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="19"/>
+      <c r="AG7" s="19"/>
+      <c r="AH7" s="19"/>
+      <c r="AI7" s="19"/>
+      <c r="AJ7" s="19"/>
       <c r="AO7" s="4"/>
-      <c r="AQ7" s="39"/>
-      <c r="AR7" s="39"/>
-      <c r="AS7" s="39"/>
-      <c r="AT7" s="39"/>
-      <c r="AU7" s="39"/>
-      <c r="AV7" s="39"/>
-      <c r="AW7" s="39"/>
-      <c r="AX7" s="39"/>
-      <c r="AY7" s="39"/>
-      <c r="AZ7" s="39"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
+      <c r="AT7" s="40"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="40"/>
+      <c r="AW7" s="40"/>
+      <c r="AX7" s="40"/>
+      <c r="AY7" s="40"/>
+      <c r="AZ7" s="40"/>
     </row>
     <row r="8" spans="1:52" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="51"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="51"/>
-      <c r="AH8" s="51"/>
-      <c r="AI8" s="51"/>
-      <c r="AJ8" s="51"/>
-      <c r="AK8" s="51"/>
-      <c r="AL8" s="51"/>
-      <c r="AM8" s="51"/>
-      <c r="AN8" s="51"/>
-      <c r="AO8" s="51"/>
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="48"/>
+      <c r="Z8" s="48"/>
+      <c r="AA8" s="48"/>
+      <c r="AB8" s="48"/>
+      <c r="AC8" s="48"/>
+      <c r="AD8" s="48"/>
+      <c r="AE8" s="48"/>
+      <c r="AF8" s="48"/>
+      <c r="AG8" s="48"/>
+      <c r="AH8" s="48"/>
+      <c r="AI8" s="48"/>
+      <c r="AJ8" s="48"/>
+      <c r="AK8" s="48"/>
+      <c r="AL8" s="48"/>
+      <c r="AM8" s="48"/>
+      <c r="AN8" s="48"/>
+      <c r="AO8" s="48"/>
       <c r="AP8" s="6"/>
-      <c r="AQ8" s="39"/>
-      <c r="AR8" s="39"/>
-      <c r="AS8" s="39"/>
-      <c r="AT8" s="39"/>
-      <c r="AU8" s="39"/>
-      <c r="AV8" s="39"/>
-      <c r="AW8" s="39"/>
-      <c r="AX8" s="39"/>
-      <c r="AY8" s="39"/>
-      <c r="AZ8" s="39"/>
+      <c r="AQ8" s="40"/>
+      <c r="AR8" s="40"/>
+      <c r="AS8" s="40"/>
+      <c r="AT8" s="40"/>
+      <c r="AU8" s="40"/>
+      <c r="AV8" s="40"/>
+      <c r="AW8" s="40"/>
+      <c r="AX8" s="40"/>
+      <c r="AY8" s="40"/>
+      <c r="AZ8" s="40"/>
     </row>
     <row r="9" spans="1:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
-      <c r="I9" s="27" t="s">
-        <v>28</v>
+      <c r="I9" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
@@ -1181,16 +1177,16 @@
         <v>5</v>
       </c>
       <c r="AP9" s="5"/>
-      <c r="AQ9" s="39"/>
-      <c r="AR9" s="39"/>
-      <c r="AS9" s="39"/>
-      <c r="AT9" s="39"/>
-      <c r="AU9" s="39"/>
-      <c r="AV9" s="39"/>
-      <c r="AW9" s="39"/>
-      <c r="AX9" s="39"/>
-      <c r="AY9" s="39"/>
-      <c r="AZ9" s="39"/>
+      <c r="AQ9" s="40"/>
+      <c r="AR9" s="40"/>
+      <c r="AS9" s="40"/>
+      <c r="AT9" s="40"/>
+      <c r="AU9" s="40"/>
+      <c r="AV9" s="40"/>
+      <c r="AW9" s="40"/>
+      <c r="AX9" s="40"/>
+      <c r="AY9" s="40"/>
+      <c r="AZ9" s="40"/>
     </row>
     <row r="10" spans="1:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
@@ -1229,16 +1225,16 @@
         <v>6</v>
       </c>
       <c r="AP10" s="5"/>
-      <c r="AQ10" s="39"/>
-      <c r="AR10" s="39"/>
-      <c r="AS10" s="39"/>
-      <c r="AT10" s="39"/>
-      <c r="AU10" s="39"/>
-      <c r="AV10" s="39"/>
-      <c r="AW10" s="39"/>
-      <c r="AX10" s="39"/>
-      <c r="AY10" s="39"/>
-      <c r="AZ10" s="39"/>
+      <c r="AQ10" s="40"/>
+      <c r="AR10" s="40"/>
+      <c r="AS10" s="40"/>
+      <c r="AT10" s="40"/>
+      <c r="AU10" s="40"/>
+      <c r="AV10" s="40"/>
+      <c r="AW10" s="40"/>
+      <c r="AX10" s="40"/>
+      <c r="AY10" s="40"/>
+      <c r="AZ10" s="40"/>
     </row>
     <row r="11" spans="1:52" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
@@ -1276,18 +1272,18 @@
       <c r="AN11" s="8"/>
       <c r="AO11" s="4"/>
       <c r="AP11" s="5"/>
-      <c r="AQ11" s="57" t="s">
+      <c r="AQ11" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="AR11" s="57"/>
-      <c r="AS11" s="57"/>
-      <c r="AT11" s="57"/>
-      <c r="AU11" s="57"/>
-      <c r="AV11" s="57"/>
-      <c r="AW11" s="57"/>
-      <c r="AX11" s="57"/>
-      <c r="AY11" s="57"/>
-      <c r="AZ11" s="57"/>
+      <c r="AR11" s="49"/>
+      <c r="AS11" s="49"/>
+      <c r="AT11" s="49"/>
+      <c r="AU11" s="49"/>
+      <c r="AV11" s="49"/>
+      <c r="AW11" s="49"/>
+      <c r="AX11" s="49"/>
+      <c r="AY11" s="49"/>
+      <c r="AZ11" s="49"/>
     </row>
     <row r="12" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
@@ -1299,18 +1295,18 @@
       <c r="G12" s="2"/>
       <c r="AI12" s="12"/>
       <c r="AJ12" s="13"/>
-      <c r="AQ12" s="40" t="s">
+      <c r="AQ12" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="AR12" s="40"/>
-      <c r="AS12" s="40"/>
-      <c r="AT12" s="40"/>
-      <c r="AU12" s="40"/>
-      <c r="AV12" s="40"/>
-      <c r="AW12" s="40"/>
-      <c r="AX12" s="40"/>
-      <c r="AY12" s="40"/>
-      <c r="AZ12" s="40"/>
+      <c r="AR12" s="50"/>
+      <c r="AS12" s="50"/>
+      <c r="AT12" s="50"/>
+      <c r="AU12" s="50"/>
+      <c r="AV12" s="50"/>
+      <c r="AW12" s="50"/>
+      <c r="AX12" s="50"/>
+      <c r="AY12" s="50"/>
+      <c r="AZ12" s="50"/>
     </row>
     <row r="13" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
@@ -1325,19 +1321,19 @@
       <c r="AK13" s="8"/>
       <c r="AL13" s="8"/>
       <c r="AM13" s="8"/>
-      <c r="AN13" s="53"/>
-      <c r="AO13" s="53"/>
-      <c r="AP13" s="53"/>
-      <c r="AQ13" s="53"/>
-      <c r="AR13" s="53"/>
-      <c r="AS13" s="53"/>
-      <c r="AT13" s="53"/>
-      <c r="AU13" s="53"/>
-      <c r="AV13" s="53"/>
-      <c r="AW13" s="53"/>
-      <c r="AX13" s="53"/>
-      <c r="AY13" s="53"/>
-      <c r="AZ13" s="53"/>
+      <c r="AN13" s="51"/>
+      <c r="AO13" s="51"/>
+      <c r="AP13" s="51"/>
+      <c r="AQ13" s="51"/>
+      <c r="AR13" s="51"/>
+      <c r="AS13" s="51"/>
+      <c r="AT13" s="51"/>
+      <c r="AU13" s="51"/>
+      <c r="AV13" s="51"/>
+      <c r="AW13" s="51"/>
+      <c r="AX13" s="51"/>
+      <c r="AY13" s="51"/>
+      <c r="AZ13" s="51"/>
     </row>
     <row r="14" spans="1:52" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
@@ -1353,199 +1349,199 @@
       <c r="N14" s="16"/>
       <c r="O14" s="16"/>
       <c r="P14" s="16"/>
-      <c r="Q14" s="41" t="s">
+      <c r="Q14" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="44"/>
+      <c r="W14" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="41"/>
-      <c r="W14" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="41"/>
-      <c r="Z14" s="41"/>
-      <c r="AA14" s="41"/>
-      <c r="AB14" s="41"/>
-      <c r="AC14" s="50" t="s">
+      <c r="X14" s="44"/>
+      <c r="Y14" s="44"/>
+      <c r="Z14" s="44"/>
+      <c r="AA14" s="44"/>
+      <c r="AB14" s="44"/>
+      <c r="AC14" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="50"/>
-      <c r="AE14" s="50"/>
-      <c r="AF14" s="50"/>
-      <c r="AG14" s="50"/>
-      <c r="AH14" s="50"/>
-      <c r="AI14" s="50"/>
-      <c r="AJ14" s="50"/>
+      <c r="AD14" s="45"/>
+      <c r="AE14" s="45"/>
+      <c r="AF14" s="45"/>
+      <c r="AG14" s="45"/>
+      <c r="AH14" s="45"/>
+      <c r="AI14" s="45"/>
+      <c r="AJ14" s="45"/>
       <c r="AK14" s="8"/>
       <c r="AL14" s="8"/>
-      <c r="AN14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
-      <c r="AQ14" s="43"/>
-      <c r="AR14" s="43"/>
-      <c r="AS14" s="43"/>
-      <c r="AT14" s="43"/>
-      <c r="AU14" s="43"/>
-      <c r="AV14" s="43"/>
-      <c r="AW14" s="43"/>
-      <c r="AX14" s="43"/>
-      <c r="AY14" s="43"/>
-      <c r="AZ14" s="43"/>
+      <c r="AN14" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO14" s="52"/>
+      <c r="AP14" s="52"/>
+      <c r="AQ14" s="52"/>
+      <c r="AR14" s="52"/>
+      <c r="AS14" s="52"/>
+      <c r="AT14" s="52"/>
+      <c r="AU14" s="52"/>
+      <c r="AV14" s="52"/>
+      <c r="AW14" s="52"/>
+      <c r="AX14" s="52"/>
+      <c r="AY14" s="52"/>
+      <c r="AZ14" s="52"/>
     </row>
     <row r="15" spans="1:52" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="P15" s="16"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="41"/>
-      <c r="Z15" s="41"/>
-      <c r="AA15" s="41"/>
-      <c r="AB15" s="41"/>
-      <c r="AC15" s="50" t="s">
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="44"/>
+      <c r="X15" s="44"/>
+      <c r="Y15" s="44"/>
+      <c r="Z15" s="44"/>
+      <c r="AA15" s="44"/>
+      <c r="AB15" s="44"/>
+      <c r="AC15" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="AD15" s="50"/>
-      <c r="AE15" s="50"/>
-      <c r="AF15" s="50"/>
-      <c r="AG15" s="50" t="s">
+      <c r="AD15" s="45"/>
+      <c r="AE15" s="45"/>
+      <c r="AF15" s="45"/>
+      <c r="AG15" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="AH15" s="50"/>
-      <c r="AI15" s="50"/>
-      <c r="AJ15" s="50"/>
+      <c r="AH15" s="45"/>
+      <c r="AI15" s="45"/>
+      <c r="AJ15" s="45"/>
       <c r="AK15" s="8"/>
-      <c r="AL15" s="48"/>
-      <c r="AM15" s="48"/>
-      <c r="AN15" s="48"/>
-      <c r="AO15" s="48"/>
-      <c r="AP15" s="48"/>
-      <c r="AQ15" s="48"/>
-      <c r="AR15" s="21"/>
-      <c r="AS15" s="49"/>
-      <c r="AT15" s="49"/>
-      <c r="AU15" s="49"/>
-      <c r="AV15" s="49"/>
-      <c r="AW15" s="49"/>
-      <c r="AX15" s="49"/>
-      <c r="AY15" s="49"/>
-      <c r="AZ15" s="49"/>
+      <c r="AL15" s="43"/>
+      <c r="AM15" s="43"/>
+      <c r="AN15" s="43"/>
+      <c r="AO15" s="43"/>
+      <c r="AP15" s="43"/>
+      <c r="AQ15" s="43"/>
+      <c r="AR15" s="20"/>
+      <c r="AS15" s="42"/>
+      <c r="AT15" s="42"/>
+      <c r="AU15" s="42"/>
+      <c r="AV15" s="42"/>
+      <c r="AW15" s="42"/>
+      <c r="AX15" s="42"/>
+      <c r="AY15" s="42"/>
+      <c r="AZ15" s="42"/>
     </row>
     <row r="16" spans="1:52" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="56"/>
-      <c r="R16" s="56"/>
-      <c r="S16" s="56"/>
-      <c r="T16" s="56"/>
-      <c r="U16" s="56"/>
-      <c r="V16" s="56"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="56"/>
-      <c r="Y16" s="56"/>
-      <c r="Z16" s="56"/>
-      <c r="AA16" s="56"/>
-      <c r="AB16" s="56"/>
-      <c r="AC16" s="56"/>
-      <c r="AD16" s="56"/>
-      <c r="AE16" s="56"/>
-      <c r="AF16" s="56"/>
-      <c r="AG16" s="56"/>
-      <c r="AH16" s="56"/>
-      <c r="AI16" s="56"/>
-      <c r="AJ16" s="56"/>
-      <c r="AL16" s="43" t="s">
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="46"/>
+      <c r="Y16" s="46"/>
+      <c r="Z16" s="46"/>
+      <c r="AA16" s="46"/>
+      <c r="AB16" s="46"/>
+      <c r="AC16" s="46"/>
+      <c r="AD16" s="46"/>
+      <c r="AE16" s="46"/>
+      <c r="AF16" s="46"/>
+      <c r="AG16" s="46"/>
+      <c r="AH16" s="46"/>
+      <c r="AI16" s="46"/>
+      <c r="AJ16" s="46"/>
+      <c r="AL16" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM16" s="52"/>
+      <c r="AN16" s="52"/>
+      <c r="AO16" s="52"/>
+      <c r="AP16" s="52"/>
+      <c r="AQ16" s="52"/>
+      <c r="AR16" s="15"/>
+      <c r="AS16" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="AM16" s="43"/>
-      <c r="AN16" s="43"/>
-      <c r="AO16" s="43"/>
-      <c r="AP16" s="43"/>
-      <c r="AQ16" s="43"/>
-      <c r="AR16" s="15"/>
-      <c r="AS16" s="42" t="s">
+      <c r="AT16" s="56"/>
+      <c r="AU16" s="56"/>
+      <c r="AV16" s="56"/>
+      <c r="AW16" s="56"/>
+      <c r="AX16" s="56"/>
+      <c r="AY16" s="56"/>
+      <c r="AZ16" s="56"/>
+    </row>
+    <row r="17" spans="1:52" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="55"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="55"/>
+      <c r="R17" s="27"/>
+      <c r="AL17" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM17" s="23"/>
+      <c r="AN17" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO17" s="47"/>
+      <c r="AP17" s="47"/>
+      <c r="AQ17" s="47"/>
+      <c r="AR17" s="47"/>
+      <c r="AS17" s="47"/>
+      <c r="AT17" s="47"/>
+      <c r="AU17" s="47"/>
+      <c r="AV17" s="24"/>
+      <c r="AW17" s="47"/>
+      <c r="AX17" s="47"/>
+      <c r="AY17" s="47"/>
+      <c r="AZ17" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="AT16" s="42"/>
-      <c r="AU16" s="42"/>
-      <c r="AV16" s="42"/>
-      <c r="AW16" s="42"/>
-      <c r="AX16" s="42"/>
-      <c r="AY16" s="42"/>
-      <c r="AZ16" s="42"/>
-    </row>
-    <row r="17" spans="1:52" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="28"/>
-      <c r="AL17" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM17" s="24"/>
-      <c r="AN17" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="AO17" s="44"/>
-      <c r="AP17" s="44"/>
-      <c r="AQ17" s="44"/>
-      <c r="AR17" s="44"/>
-      <c r="AS17" s="44"/>
-      <c r="AT17" s="44"/>
-      <c r="AU17" s="44"/>
-      <c r="AV17" s="25"/>
-      <c r="AW17" s="44"/>
-      <c r="AX17" s="44"/>
-      <c r="AY17" s="44"/>
-      <c r="AZ17" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:52" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
@@ -1567,13 +1563,13 @@
       <c r="Q19" s="38"/>
       <c r="R19" s="38"/>
       <c r="S19" s="38" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="T19" s="38"/>
       <c r="U19" s="38"/>
       <c r="V19" s="38"/>
       <c r="W19" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X19" s="33"/>
       <c r="Y19" s="33"/>
@@ -1582,7 +1578,7 @@
       <c r="AB19" s="33"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AE19" s="33"/>
       <c r="AF19" s="33"/>
@@ -1591,7 +1587,7 @@
       <c r="AI19" s="33"/>
       <c r="AJ19" s="33"/>
       <c r="AK19" s="33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AL19" s="33"/>
       <c r="AM19" s="33"/>
@@ -1601,7 +1597,7 @@
       <c r="AQ19" s="33"/>
       <c r="AR19" s="33"/>
       <c r="AS19" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AT19" s="33"/>
       <c r="AU19" s="33"/>
@@ -1828,10 +1824,10 @@
       <c r="AZ23" s="33"/>
     </row>
     <row r="24" spans="1:52" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="34"/>
@@ -1846,46 +1842,46 @@
       <c r="P24" s="34"/>
       <c r="Q24" s="34"/>
       <c r="R24" s="34"/>
-      <c r="S24" s="36"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="36"/>
-      <c r="V24" s="36"/>
-      <c r="W24" s="29"/>
-      <c r="X24" s="29"/>
-      <c r="Y24" s="29"/>
-      <c r="Z24" s="29"/>
-      <c r="AA24" s="29"/>
-      <c r="AB24" s="29"/>
-      <c r="AC24" s="29"/>
-      <c r="AD24" s="29"/>
-      <c r="AE24" s="29"/>
-      <c r="AF24" s="29"/>
-      <c r="AG24" s="29"/>
-      <c r="AH24" s="29"/>
-      <c r="AI24" s="29"/>
-      <c r="AJ24" s="29"/>
-      <c r="AK24" s="29"/>
-      <c r="AL24" s="29"/>
-      <c r="AM24" s="29"/>
-      <c r="AN24" s="29"/>
-      <c r="AO24" s="29"/>
-      <c r="AP24" s="29"/>
-      <c r="AQ24" s="29"/>
-      <c r="AR24" s="29"/>
-      <c r="AS24" s="29"/>
-      <c r="AT24" s="29"/>
-      <c r="AU24" s="29"/>
-      <c r="AV24" s="29"/>
-      <c r="AW24" s="29"/>
-      <c r="AX24" s="29"/>
-      <c r="AY24" s="29"/>
-      <c r="AZ24" s="29"/>
+      <c r="S24" s="37"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="37"/>
+      <c r="V24" s="37"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30"/>
+      <c r="AG24" s="30"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="30"/>
+      <c r="AM24" s="30"/>
+      <c r="AN24" s="30"/>
+      <c r="AO24" s="30"/>
+      <c r="AP24" s="30"/>
+      <c r="AQ24" s="30"/>
+      <c r="AR24" s="30"/>
+      <c r="AS24" s="30"/>
+      <c r="AT24" s="30"/>
+      <c r="AU24" s="30"/>
+      <c r="AV24" s="30"/>
+      <c r="AW24" s="30"/>
+      <c r="AX24" s="30"/>
+      <c r="AY24" s="30"/>
+      <c r="AZ24" s="30"/>
     </row>
     <row r="25" spans="1:52" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
       <c r="E25" s="34"/>
       <c r="F25" s="34"/>
       <c r="G25" s="34"/>
@@ -1900,46 +1896,46 @@
       <c r="P25" s="34"/>
       <c r="Q25" s="34"/>
       <c r="R25" s="34"/>
-      <c r="S25" s="36"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="36"/>
-      <c r="V25" s="36"/>
-      <c r="W25" s="29"/>
-      <c r="X25" s="29"/>
-      <c r="Y25" s="29"/>
-      <c r="Z25" s="29"/>
-      <c r="AA25" s="29"/>
-      <c r="AB25" s="29"/>
-      <c r="AC25" s="29"/>
-      <c r="AD25" s="29"/>
-      <c r="AE25" s="29"/>
-      <c r="AF25" s="29"/>
-      <c r="AG25" s="29"/>
-      <c r="AH25" s="29"/>
-      <c r="AI25" s="29"/>
-      <c r="AJ25" s="29"/>
-      <c r="AK25" s="29"/>
-      <c r="AL25" s="29"/>
-      <c r="AM25" s="29"/>
-      <c r="AN25" s="29"/>
-      <c r="AO25" s="29"/>
-      <c r="AP25" s="29"/>
-      <c r="AQ25" s="29"/>
-      <c r="AR25" s="29"/>
-      <c r="AS25" s="29"/>
-      <c r="AT25" s="29"/>
-      <c r="AU25" s="29"/>
-      <c r="AV25" s="29"/>
-      <c r="AW25" s="29"/>
-      <c r="AX25" s="29"/>
-      <c r="AY25" s="29"/>
-      <c r="AZ25" s="29"/>
+      <c r="S25" s="37"/>
+      <c r="T25" s="37"/>
+      <c r="U25" s="37"/>
+      <c r="V25" s="37"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="30"/>
+      <c r="AA25" s="30"/>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="30"/>
+      <c r="AD25" s="30"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
+      <c r="AG25" s="30"/>
+      <c r="AH25" s="30"/>
+      <c r="AI25" s="30"/>
+      <c r="AJ25" s="30"/>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="30"/>
+      <c r="AM25" s="30"/>
+      <c r="AN25" s="30"/>
+      <c r="AO25" s="30"/>
+      <c r="AP25" s="30"/>
+      <c r="AQ25" s="30"/>
+      <c r="AR25" s="30"/>
+      <c r="AS25" s="30"/>
+      <c r="AT25" s="30"/>
+      <c r="AU25" s="30"/>
+      <c r="AV25" s="30"/>
+      <c r="AW25" s="30"/>
+      <c r="AX25" s="30"/>
+      <c r="AY25" s="30"/>
+      <c r="AZ25" s="30"/>
     </row>
     <row r="26" spans="1:52" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
       <c r="E26" s="34"/>
       <c r="F26" s="34"/>
       <c r="G26" s="34"/>
@@ -1954,46 +1950,46 @@
       <c r="P26" s="34"/>
       <c r="Q26" s="34"/>
       <c r="R26" s="34"/>
-      <c r="S26" s="36"/>
-      <c r="T26" s="36"/>
-      <c r="U26" s="36"/>
-      <c r="V26" s="36"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
-      <c r="AG26" s="29"/>
-      <c r="AH26" s="29"/>
-      <c r="AI26" s="29"/>
-      <c r="AJ26" s="29"/>
-      <c r="AK26" s="29"/>
-      <c r="AL26" s="29"/>
-      <c r="AM26" s="29"/>
-      <c r="AN26" s="29"/>
-      <c r="AO26" s="29"/>
-      <c r="AP26" s="29"/>
-      <c r="AQ26" s="29"/>
-      <c r="AR26" s="29"/>
-      <c r="AS26" s="29"/>
-      <c r="AT26" s="29"/>
-      <c r="AU26" s="29"/>
-      <c r="AV26" s="29"/>
-      <c r="AW26" s="29"/>
-      <c r="AX26" s="29"/>
-      <c r="AY26" s="29"/>
-      <c r="AZ26" s="29"/>
+      <c r="S26" s="37"/>
+      <c r="T26" s="37"/>
+      <c r="U26" s="37"/>
+      <c r="V26" s="37"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
+      <c r="AG26" s="30"/>
+      <c r="AH26" s="30"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="30"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="30"/>
+      <c r="AM26" s="30"/>
+      <c r="AN26" s="30"/>
+      <c r="AO26" s="30"/>
+      <c r="AP26" s="30"/>
+      <c r="AQ26" s="30"/>
+      <c r="AR26" s="30"/>
+      <c r="AS26" s="30"/>
+      <c r="AT26" s="30"/>
+      <c r="AU26" s="30"/>
+      <c r="AV26" s="30"/>
+      <c r="AW26" s="30"/>
+      <c r="AX26" s="30"/>
+      <c r="AY26" s="30"/>
+      <c r="AZ26" s="30"/>
     </row>
     <row r="27" spans="1:52" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
       <c r="G27" s="34"/>
@@ -2008,46 +2004,46 @@
       <c r="P27" s="34"/>
       <c r="Q27" s="34"/>
       <c r="R27" s="34"/>
-      <c r="S27" s="36"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="36"/>
-      <c r="V27" s="36"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="29"/>
-      <c r="Y27" s="29"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="29"/>
-      <c r="AE27" s="29"/>
-      <c r="AF27" s="29"/>
-      <c r="AG27" s="29"/>
-      <c r="AH27" s="29"/>
-      <c r="AI27" s="29"/>
-      <c r="AJ27" s="29"/>
-      <c r="AK27" s="29"/>
-      <c r="AL27" s="29"/>
-      <c r="AM27" s="29"/>
-      <c r="AN27" s="29"/>
-      <c r="AO27" s="29"/>
-      <c r="AP27" s="29"/>
-      <c r="AQ27" s="29"/>
-      <c r="AR27" s="29"/>
-      <c r="AS27" s="29"/>
-      <c r="AT27" s="29"/>
-      <c r="AU27" s="29"/>
-      <c r="AV27" s="29"/>
-      <c r="AW27" s="29"/>
-      <c r="AX27" s="29"/>
-      <c r="AY27" s="29"/>
-      <c r="AZ27" s="29"/>
+      <c r="S27" s="37"/>
+      <c r="T27" s="37"/>
+      <c r="U27" s="37"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="30"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
+      <c r="AM27" s="30"/>
+      <c r="AN27" s="30"/>
+      <c r="AO27" s="30"/>
+      <c r="AP27" s="30"/>
+      <c r="AQ27" s="30"/>
+      <c r="AR27" s="30"/>
+      <c r="AS27" s="30"/>
+      <c r="AT27" s="30"/>
+      <c r="AU27" s="30"/>
+      <c r="AV27" s="30"/>
+      <c r="AW27" s="30"/>
+      <c r="AX27" s="30"/>
+      <c r="AY27" s="30"/>
+      <c r="AZ27" s="30"/>
     </row>
     <row r="28" spans="1:52" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
       <c r="E28" s="34"/>
       <c r="F28" s="34"/>
       <c r="G28" s="34"/>
@@ -2062,46 +2058,46 @@
       <c r="P28" s="34"/>
       <c r="Q28" s="34"/>
       <c r="R28" s="34"/>
-      <c r="S28" s="36"/>
-      <c r="T28" s="36"/>
-      <c r="U28" s="36"/>
-      <c r="V28" s="36"/>
-      <c r="W28" s="29"/>
-      <c r="X28" s="29"/>
-      <c r="Y28" s="29"/>
-      <c r="Z28" s="29"/>
-      <c r="AA28" s="29"/>
-      <c r="AB28" s="29"/>
-      <c r="AC28" s="29"/>
-      <c r="AD28" s="29"/>
-      <c r="AE28" s="29"/>
-      <c r="AF28" s="29"/>
-      <c r="AG28" s="29"/>
-      <c r="AH28" s="29"/>
-      <c r="AI28" s="29"/>
-      <c r="AJ28" s="29"/>
-      <c r="AK28" s="29"/>
-      <c r="AL28" s="29"/>
-      <c r="AM28" s="29"/>
-      <c r="AN28" s="29"/>
-      <c r="AO28" s="29"/>
-      <c r="AP28" s="29"/>
-      <c r="AQ28" s="29"/>
-      <c r="AR28" s="29"/>
-      <c r="AS28" s="29"/>
-      <c r="AT28" s="29"/>
-      <c r="AU28" s="29"/>
-      <c r="AV28" s="29"/>
-      <c r="AW28" s="29"/>
-      <c r="AX28" s="29"/>
-      <c r="AY28" s="29"/>
-      <c r="AZ28" s="29"/>
+      <c r="S28" s="37"/>
+      <c r="T28" s="37"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="30"/>
+      <c r="AM28" s="30"/>
+      <c r="AN28" s="30"/>
+      <c r="AO28" s="30"/>
+      <c r="AP28" s="30"/>
+      <c r="AQ28" s="30"/>
+      <c r="AR28" s="30"/>
+      <c r="AS28" s="30"/>
+      <c r="AT28" s="30"/>
+      <c r="AU28" s="30"/>
+      <c r="AV28" s="30"/>
+      <c r="AW28" s="30"/>
+      <c r="AX28" s="30"/>
+      <c r="AY28" s="30"/>
+      <c r="AZ28" s="30"/>
     </row>
     <row r="29" spans="1:52" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
       <c r="E29" s="34"/>
       <c r="F29" s="34"/>
       <c r="G29" s="34"/>
@@ -2116,46 +2112,46 @@
       <c r="P29" s="34"/>
       <c r="Q29" s="34"/>
       <c r="R29" s="34"/>
-      <c r="S29" s="36"/>
-      <c r="T29" s="36"/>
-      <c r="U29" s="36"/>
-      <c r="V29" s="36"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="29"/>
-      <c r="AF29" s="29"/>
-      <c r="AG29" s="29"/>
-      <c r="AH29" s="29"/>
-      <c r="AI29" s="29"/>
-      <c r="AJ29" s="29"/>
-      <c r="AK29" s="29"/>
-      <c r="AL29" s="29"/>
-      <c r="AM29" s="29"/>
-      <c r="AN29" s="29"/>
-      <c r="AO29" s="29"/>
-      <c r="AP29" s="29"/>
-      <c r="AQ29" s="29"/>
-      <c r="AR29" s="29"/>
-      <c r="AS29" s="29"/>
-      <c r="AT29" s="29"/>
-      <c r="AU29" s="29"/>
-      <c r="AV29" s="29"/>
-      <c r="AW29" s="29"/>
-      <c r="AX29" s="29"/>
-      <c r="AY29" s="29"/>
-      <c r="AZ29" s="29"/>
+      <c r="S29" s="37"/>
+      <c r="T29" s="37"/>
+      <c r="U29" s="37"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
+      <c r="AG29" s="30"/>
+      <c r="AH29" s="30"/>
+      <c r="AI29" s="30"/>
+      <c r="AJ29" s="30"/>
+      <c r="AK29" s="30"/>
+      <c r="AL29" s="30"/>
+      <c r="AM29" s="30"/>
+      <c r="AN29" s="30"/>
+      <c r="AO29" s="30"/>
+      <c r="AP29" s="30"/>
+      <c r="AQ29" s="30"/>
+      <c r="AR29" s="30"/>
+      <c r="AS29" s="30"/>
+      <c r="AT29" s="30"/>
+      <c r="AU29" s="30"/>
+      <c r="AV29" s="30"/>
+      <c r="AW29" s="30"/>
+      <c r="AX29" s="30"/>
+      <c r="AY29" s="30"/>
+      <c r="AZ29" s="30"/>
     </row>
     <row r="30" spans="1:52" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
       <c r="E30" s="34"/>
       <c r="F30" s="34"/>
       <c r="G30" s="34"/>
@@ -2170,46 +2166,46 @@
       <c r="P30" s="34"/>
       <c r="Q30" s="34"/>
       <c r="R30" s="34"/>
-      <c r="S30" s="36"/>
-      <c r="T30" s="36"/>
-      <c r="U30" s="36"/>
-      <c r="V30" s="36"/>
-      <c r="W30" s="29"/>
-      <c r="X30" s="29"/>
-      <c r="Y30" s="29"/>
-      <c r="Z30" s="29"/>
-      <c r="AA30" s="29"/>
-      <c r="AB30" s="29"/>
-      <c r="AC30" s="29"/>
-      <c r="AD30" s="29"/>
-      <c r="AE30" s="29"/>
-      <c r="AF30" s="29"/>
-      <c r="AG30" s="29"/>
-      <c r="AH30" s="29"/>
-      <c r="AI30" s="29"/>
-      <c r="AJ30" s="29"/>
-      <c r="AK30" s="29"/>
-      <c r="AL30" s="29"/>
-      <c r="AM30" s="29"/>
-      <c r="AN30" s="29"/>
-      <c r="AO30" s="29"/>
-      <c r="AP30" s="29"/>
-      <c r="AQ30" s="29"/>
-      <c r="AR30" s="29"/>
-      <c r="AS30" s="29"/>
-      <c r="AT30" s="29"/>
-      <c r="AU30" s="29"/>
-      <c r="AV30" s="29"/>
-      <c r="AW30" s="29"/>
-      <c r="AX30" s="29"/>
-      <c r="AY30" s="29"/>
-      <c r="AZ30" s="29"/>
+      <c r="S30" s="37"/>
+      <c r="T30" s="37"/>
+      <c r="U30" s="37"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
+      <c r="AG30" s="30"/>
+      <c r="AH30" s="30"/>
+      <c r="AI30" s="30"/>
+      <c r="AJ30" s="30"/>
+      <c r="AK30" s="30"/>
+      <c r="AL30" s="30"/>
+      <c r="AM30" s="30"/>
+      <c r="AN30" s="30"/>
+      <c r="AO30" s="30"/>
+      <c r="AP30" s="30"/>
+      <c r="AQ30" s="30"/>
+      <c r="AR30" s="30"/>
+      <c r="AS30" s="30"/>
+      <c r="AT30" s="30"/>
+      <c r="AU30" s="30"/>
+      <c r="AV30" s="30"/>
+      <c r="AW30" s="30"/>
+      <c r="AX30" s="30"/>
+      <c r="AY30" s="30"/>
+      <c r="AZ30" s="30"/>
     </row>
     <row r="31" spans="1:52" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
       <c r="E31" s="34"/>
       <c r="F31" s="34"/>
       <c r="G31" s="34"/>
@@ -2224,85 +2220,85 @@
       <c r="P31" s="34"/>
       <c r="Q31" s="34"/>
       <c r="R31" s="34"/>
-      <c r="S31" s="36"/>
-      <c r="T31" s="36"/>
-      <c r="U31" s="36"/>
-      <c r="V31" s="36"/>
-      <c r="W31" s="29"/>
-      <c r="X31" s="29"/>
-      <c r="Y31" s="29"/>
-      <c r="Z31" s="29"/>
-      <c r="AA31" s="29"/>
-      <c r="AB31" s="29"/>
-      <c r="AC31" s="29"/>
-      <c r="AD31" s="29"/>
-      <c r="AE31" s="29"/>
-      <c r="AF31" s="29"/>
-      <c r="AG31" s="29"/>
-      <c r="AH31" s="29"/>
-      <c r="AI31" s="29"/>
-      <c r="AJ31" s="29"/>
-      <c r="AK31" s="29"/>
-      <c r="AL31" s="29"/>
-      <c r="AM31" s="29"/>
-      <c r="AN31" s="29"/>
-      <c r="AO31" s="29"/>
-      <c r="AP31" s="29"/>
-      <c r="AQ31" s="29"/>
-      <c r="AR31" s="29"/>
-      <c r="AS31" s="29"/>
-      <c r="AT31" s="29"/>
-      <c r="AU31" s="29"/>
-      <c r="AV31" s="29"/>
-      <c r="AW31" s="29"/>
-      <c r="AX31" s="29"/>
-      <c r="AY31" s="29"/>
-      <c r="AZ31" s="29"/>
+      <c r="S31" s="37"/>
+      <c r="T31" s="37"/>
+      <c r="U31" s="37"/>
+      <c r="V31" s="37"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="30"/>
+      <c r="AD31" s="30"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="30"/>
+      <c r="AG31" s="30"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="30"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="30"/>
+      <c r="AM31" s="30"/>
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="30"/>
+      <c r="AP31" s="30"/>
+      <c r="AQ31" s="30"/>
+      <c r="AR31" s="30"/>
+      <c r="AS31" s="30"/>
+      <c r="AT31" s="30"/>
+      <c r="AU31" s="30"/>
+      <c r="AV31" s="30"/>
+      <c r="AW31" s="30"/>
+      <c r="AX31" s="30"/>
+      <c r="AY31" s="30"/>
+      <c r="AZ31" s="30"/>
     </row>
     <row r="32" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="S32" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="T32" s="52"/>
-      <c r="U32" s="52"/>
-      <c r="V32" s="52"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="29"/>
-      <c r="AE32" s="29"/>
-      <c r="AF32" s="29"/>
-      <c r="AG32" s="29"/>
-      <c r="AH32" s="29"/>
-      <c r="AI32" s="29"/>
-      <c r="AJ32" s="29"/>
-      <c r="AK32" s="29"/>
-      <c r="AL32" s="29"/>
-      <c r="AM32" s="29"/>
-      <c r="AN32" s="29"/>
-      <c r="AO32" s="29"/>
-      <c r="AP32" s="29"/>
-      <c r="AQ32" s="29"/>
-      <c r="AR32" s="29"/>
-      <c r="AS32" s="29"/>
-      <c r="AT32" s="29"/>
-      <c r="AU32" s="29"/>
-      <c r="AV32" s="29"/>
-      <c r="AW32" s="29"/>
-      <c r="AX32" s="29"/>
-      <c r="AY32" s="29"/>
-      <c r="AZ32" s="29"/>
-    </row>
-    <row r="34" spans="1:52" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A34" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:52" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="S32" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
+      <c r="AG32" s="30"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="30"/>
+      <c r="AJ32" s="30"/>
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="30"/>
+      <c r="AM32" s="30"/>
+      <c r="AN32" s="30"/>
+      <c r="AO32" s="30"/>
+      <c r="AP32" s="30"/>
+      <c r="AQ32" s="30"/>
+      <c r="AR32" s="30"/>
+      <c r="AS32" s="30"/>
+      <c r="AT32" s="30"/>
+      <c r="AU32" s="30"/>
+      <c r="AV32" s="30"/>
+      <c r="AW32" s="30"/>
+      <c r="AX32" s="30"/>
+      <c r="AY32" s="30"/>
+      <c r="AZ32" s="30"/>
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.2">
+      <c r="A34" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="33"/>
       <c r="B36" s="33"/>
@@ -2334,32 +2330,32 @@
       <c r="AB36" s="33"/>
       <c r="AC36" s="33"/>
       <c r="AD36" s="33"/>
-      <c r="AE36" s="32" t="s">
+      <c r="AE36" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF36" s="31"/>
+      <c r="AG36" s="31"/>
+      <c r="AH36" s="31"/>
+      <c r="AI36" s="31"/>
+      <c r="AJ36" s="31"/>
+      <c r="AK36" s="31"/>
+      <c r="AL36" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="AF36" s="32"/>
-      <c r="AG36" s="32"/>
-      <c r="AH36" s="32"/>
-      <c r="AI36" s="32"/>
-      <c r="AJ36" s="32"/>
-      <c r="AK36" s="32"/>
-      <c r="AL36" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="AM36" s="32"/>
-      <c r="AN36" s="32"/>
-      <c r="AO36" s="32"/>
-      <c r="AP36" s="32"/>
-      <c r="AQ36" s="32"/>
-      <c r="AR36" s="32"/>
-      <c r="AS36" s="32"/>
-      <c r="AT36" s="32"/>
-      <c r="AU36" s="32"/>
-      <c r="AV36" s="32"/>
-      <c r="AW36" s="32"/>
-      <c r="AX36" s="32"/>
-      <c r="AY36" s="32"/>
-      <c r="AZ36" s="32"/>
+      <c r="AM36" s="31"/>
+      <c r="AN36" s="31"/>
+      <c r="AO36" s="31"/>
+      <c r="AP36" s="31"/>
+      <c r="AQ36" s="31"/>
+      <c r="AR36" s="31"/>
+      <c r="AS36" s="31"/>
+      <c r="AT36" s="31"/>
+      <c r="AU36" s="31"/>
+      <c r="AV36" s="31"/>
+      <c r="AW36" s="31"/>
+      <c r="AX36" s="31"/>
+      <c r="AY36" s="31"/>
+      <c r="AZ36" s="31"/>
     </row>
     <row r="37" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="33"/>
@@ -2392,32 +2388,32 @@
       <c r="AB37" s="33"/>
       <c r="AC37" s="33"/>
       <c r="AD37" s="33"/>
-      <c r="AE37" s="32"/>
-      <c r="AF37" s="32"/>
-      <c r="AG37" s="32"/>
-      <c r="AH37" s="32"/>
-      <c r="AI37" s="32"/>
-      <c r="AJ37" s="32"/>
-      <c r="AK37" s="32"/>
-      <c r="AL37" s="32"/>
-      <c r="AM37" s="32"/>
-      <c r="AN37" s="32"/>
-      <c r="AO37" s="32"/>
-      <c r="AP37" s="32"/>
-      <c r="AQ37" s="32"/>
-      <c r="AR37" s="32"/>
-      <c r="AS37" s="32"/>
-      <c r="AT37" s="32"/>
-      <c r="AU37" s="32"/>
-      <c r="AV37" s="32"/>
-      <c r="AW37" s="32"/>
-      <c r="AX37" s="32"/>
-      <c r="AY37" s="32"/>
-      <c r="AZ37" s="32"/>
+      <c r="AE37" s="31"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="31"/>
+      <c r="AH37" s="31"/>
+      <c r="AI37" s="31"/>
+      <c r="AJ37" s="31"/>
+      <c r="AK37" s="31"/>
+      <c r="AL37" s="31"/>
+      <c r="AM37" s="31"/>
+      <c r="AN37" s="31"/>
+      <c r="AO37" s="31"/>
+      <c r="AP37" s="31"/>
+      <c r="AQ37" s="31"/>
+      <c r="AR37" s="31"/>
+      <c r="AS37" s="31"/>
+      <c r="AT37" s="31"/>
+      <c r="AU37" s="31"/>
+      <c r="AV37" s="31"/>
+      <c r="AW37" s="31"/>
+      <c r="AX37" s="31"/>
+      <c r="AY37" s="31"/>
+      <c r="AZ37" s="31"/>
     </row>
     <row r="38" spans="1:52" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="34"/>
       <c r="C38" s="34"/>
@@ -2448,146 +2444,146 @@
       <c r="AB38" s="34"/>
       <c r="AC38" s="34"/>
       <c r="AD38" s="34"/>
-      <c r="AE38" s="54"/>
-      <c r="AF38" s="54"/>
-      <c r="AG38" s="54"/>
-      <c r="AH38" s="54"/>
-      <c r="AI38" s="54"/>
-      <c r="AJ38" s="54"/>
-      <c r="AK38" s="54"/>
-      <c r="AL38" s="54"/>
-      <c r="AM38" s="54"/>
-      <c r="AN38" s="54"/>
-      <c r="AO38" s="54"/>
-      <c r="AP38" s="54"/>
-      <c r="AQ38" s="54"/>
-      <c r="AR38" s="54"/>
-      <c r="AS38" s="54"/>
-      <c r="AT38" s="54"/>
-      <c r="AU38" s="54"/>
-      <c r="AV38" s="54"/>
-      <c r="AW38" s="54"/>
-      <c r="AX38" s="54"/>
-      <c r="AY38" s="54"/>
-      <c r="AZ38" s="54"/>
+      <c r="AE38" s="35"/>
+      <c r="AF38" s="35"/>
+      <c r="AG38" s="35"/>
+      <c r="AH38" s="35"/>
+      <c r="AI38" s="35"/>
+      <c r="AJ38" s="35"/>
+      <c r="AK38" s="35"/>
+      <c r="AL38" s="35"/>
+      <c r="AM38" s="35"/>
+      <c r="AN38" s="35"/>
+      <c r="AO38" s="35"/>
+      <c r="AP38" s="35"/>
+      <c r="AQ38" s="35"/>
+      <c r="AR38" s="35"/>
+      <c r="AS38" s="35"/>
+      <c r="AT38" s="35"/>
+      <c r="AU38" s="35"/>
+      <c r="AV38" s="35"/>
+      <c r="AW38" s="35"/>
+      <c r="AX38" s="35"/>
+      <c r="AY38" s="35"/>
+      <c r="AZ38" s="35"/>
     </row>
     <row r="39" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="29"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="29" t="s">
+      <c r="A39" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R39" s="30"/>
+      <c r="S39" s="30"/>
+      <c r="T39" s="30"/>
+      <c r="U39" s="30"/>
+      <c r="V39" s="30"/>
+      <c r="W39" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="R39" s="29"/>
-      <c r="S39" s="29"/>
-      <c r="T39" s="29"/>
-      <c r="U39" s="29"/>
-      <c r="V39" s="29"/>
-      <c r="W39" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="X39" s="29"/>
-      <c r="Y39" s="29"/>
-      <c r="Z39" s="29"/>
-      <c r="AA39" s="29"/>
-      <c r="AB39" s="29"/>
-      <c r="AC39" s="29"/>
-      <c r="AD39" s="29"/>
-      <c r="AE39" s="54"/>
-      <c r="AF39" s="54"/>
-      <c r="AG39" s="54"/>
-      <c r="AH39" s="54"/>
-      <c r="AI39" s="54"/>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="54"/>
-      <c r="AP39" s="54"/>
-      <c r="AQ39" s="54"/>
-      <c r="AR39" s="54"/>
-      <c r="AS39" s="54"/>
-      <c r="AT39" s="54"/>
-      <c r="AU39" s="54"/>
-      <c r="AV39" s="54"/>
-      <c r="AW39" s="54"/>
-      <c r="AX39" s="54"/>
-      <c r="AY39" s="54"/>
-      <c r="AZ39" s="54"/>
+      <c r="X39" s="30"/>
+      <c r="Y39" s="30"/>
+      <c r="Z39" s="30"/>
+      <c r="AA39" s="30"/>
+      <c r="AB39" s="30"/>
+      <c r="AC39" s="30"/>
+      <c r="AD39" s="30"/>
+      <c r="AE39" s="35"/>
+      <c r="AF39" s="35"/>
+      <c r="AG39" s="35"/>
+      <c r="AH39" s="35"/>
+      <c r="AI39" s="35"/>
+      <c r="AJ39" s="35"/>
+      <c r="AK39" s="35"/>
+      <c r="AL39" s="35"/>
+      <c r="AM39" s="35"/>
+      <c r="AN39" s="35"/>
+      <c r="AO39" s="35"/>
+      <c r="AP39" s="35"/>
+      <c r="AQ39" s="35"/>
+      <c r="AR39" s="35"/>
+      <c r="AS39" s="35"/>
+      <c r="AT39" s="35"/>
+      <c r="AU39" s="35"/>
+      <c r="AV39" s="35"/>
+      <c r="AW39" s="35"/>
+      <c r="AX39" s="35"/>
+      <c r="AY39" s="35"/>
+      <c r="AZ39" s="35"/>
     </row>
     <row r="40" spans="1:52" ht="3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="AD40" s="29"/>
-      <c r="AE40" s="54"/>
-      <c r="AF40" s="54"/>
-      <c r="AG40" s="54"/>
-      <c r="AH40" s="54"/>
-      <c r="AI40" s="54"/>
-      <c r="AJ40" s="54"/>
-      <c r="AK40" s="54"/>
-      <c r="AL40" s="54"/>
-      <c r="AM40" s="54"/>
-      <c r="AN40" s="54"/>
-      <c r="AO40" s="54"/>
-      <c r="AP40" s="54"/>
-      <c r="AQ40" s="54"/>
-      <c r="AR40" s="54"/>
-      <c r="AS40" s="54"/>
-      <c r="AT40" s="54"/>
-      <c r="AU40" s="54"/>
-      <c r="AV40" s="54"/>
-      <c r="AW40" s="54"/>
-      <c r="AX40" s="54"/>
-      <c r="AY40" s="54"/>
-      <c r="AZ40" s="54"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
+      <c r="AE40" s="35"/>
+      <c r="AF40" s="35"/>
+      <c r="AG40" s="35"/>
+      <c r="AH40" s="35"/>
+      <c r="AI40" s="35"/>
+      <c r="AJ40" s="35"/>
+      <c r="AK40" s="35"/>
+      <c r="AL40" s="35"/>
+      <c r="AM40" s="35"/>
+      <c r="AN40" s="35"/>
+      <c r="AO40" s="35"/>
+      <c r="AP40" s="35"/>
+      <c r="AQ40" s="35"/>
+      <c r="AR40" s="35"/>
+      <c r="AS40" s="35"/>
+      <c r="AT40" s="35"/>
+      <c r="AU40" s="35"/>
+      <c r="AV40" s="35"/>
+      <c r="AW40" s="35"/>
+      <c r="AX40" s="35"/>
+      <c r="AY40" s="35"/>
+      <c r="AZ40" s="35"/>
     </row>
     <row r="41" spans="1:52" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="34"/>
       <c r="C41" s="34"/>
@@ -2618,202 +2614,202 @@
       <c r="AB41" s="34"/>
       <c r="AC41" s="34"/>
       <c r="AD41" s="34"/>
-      <c r="AE41" s="54"/>
-      <c r="AF41" s="54"/>
-      <c r="AG41" s="54"/>
-      <c r="AH41" s="54"/>
-      <c r="AI41" s="54"/>
-      <c r="AJ41" s="54"/>
-      <c r="AK41" s="54"/>
-      <c r="AL41" s="54"/>
-      <c r="AM41" s="54"/>
-      <c r="AN41" s="54"/>
-      <c r="AO41" s="54"/>
-      <c r="AP41" s="54"/>
-      <c r="AQ41" s="54"/>
-      <c r="AR41" s="54"/>
-      <c r="AS41" s="54"/>
-      <c r="AT41" s="54"/>
-      <c r="AU41" s="54"/>
-      <c r="AV41" s="54"/>
-      <c r="AW41" s="54"/>
-      <c r="AX41" s="54"/>
-      <c r="AY41" s="54"/>
-      <c r="AZ41" s="54"/>
+      <c r="AE41" s="35"/>
+      <c r="AF41" s="35"/>
+      <c r="AG41" s="35"/>
+      <c r="AH41" s="35"/>
+      <c r="AI41" s="35"/>
+      <c r="AJ41" s="35"/>
+      <c r="AK41" s="35"/>
+      <c r="AL41" s="35"/>
+      <c r="AM41" s="35"/>
+      <c r="AN41" s="35"/>
+      <c r="AO41" s="35"/>
+      <c r="AP41" s="35"/>
+      <c r="AQ41" s="35"/>
+      <c r="AR41" s="35"/>
+      <c r="AS41" s="35"/>
+      <c r="AT41" s="35"/>
+      <c r="AU41" s="35"/>
+      <c r="AV41" s="35"/>
+      <c r="AW41" s="35"/>
+      <c r="AX41" s="35"/>
+      <c r="AY41" s="35"/>
+      <c r="AZ41" s="35"/>
     </row>
     <row r="42" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29" t="s">
+      <c r="A42" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="R42" s="29"/>
-      <c r="S42" s="29"/>
-      <c r="T42" s="29"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
-      <c r="W42" s="29" t="s">
+      <c r="X42" s="30"/>
+      <c r="Y42" s="30"/>
+      <c r="Z42" s="30"/>
+      <c r="AA42" s="30"/>
+      <c r="AB42" s="30"/>
+      <c r="AC42" s="30"/>
+      <c r="AD42" s="30"/>
+      <c r="AE42" s="35"/>
+      <c r="AF42" s="35"/>
+      <c r="AG42" s="35"/>
+      <c r="AH42" s="35"/>
+      <c r="AI42" s="35"/>
+      <c r="AJ42" s="35"/>
+      <c r="AK42" s="35"/>
+      <c r="AL42" s="35"/>
+      <c r="AM42" s="35"/>
+      <c r="AN42" s="35"/>
+      <c r="AO42" s="35"/>
+      <c r="AP42" s="35"/>
+      <c r="AQ42" s="35"/>
+      <c r="AR42" s="35"/>
+      <c r="AS42" s="35"/>
+      <c r="AT42" s="35"/>
+      <c r="AU42" s="35"/>
+      <c r="AV42" s="35"/>
+      <c r="AW42" s="35"/>
+      <c r="AX42" s="35"/>
+      <c r="AY42" s="35"/>
+      <c r="AZ42" s="35"/>
+    </row>
+    <row r="43" spans="1:52" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
+      <c r="AE43" s="35"/>
+      <c r="AF43" s="35"/>
+      <c r="AG43" s="35"/>
+      <c r="AH43" s="35"/>
+      <c r="AI43" s="35"/>
+      <c r="AJ43" s="35"/>
+      <c r="AK43" s="35"/>
+      <c r="AL43" s="35"/>
+      <c r="AM43" s="35"/>
+      <c r="AN43" s="35"/>
+      <c r="AO43" s="35"/>
+      <c r="AP43" s="35"/>
+      <c r="AQ43" s="35"/>
+      <c r="AR43" s="35"/>
+      <c r="AS43" s="35"/>
+      <c r="AT43" s="35"/>
+      <c r="AU43" s="35"/>
+      <c r="AV43" s="35"/>
+      <c r="AW43" s="35"/>
+      <c r="AX43" s="35"/>
+      <c r="AY43" s="35"/>
+      <c r="AZ43" s="35"/>
+    </row>
+    <row r="44" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+      <c r="A44" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="X42" s="29"/>
-      <c r="Y42" s="29"/>
-      <c r="Z42" s="29"/>
-      <c r="AA42" s="29"/>
-      <c r="AB42" s="29"/>
-      <c r="AC42" s="29"/>
-      <c r="AD42" s="29"/>
-      <c r="AE42" s="54"/>
-      <c r="AF42" s="54"/>
-      <c r="AG42" s="54"/>
-      <c r="AH42" s="54"/>
-      <c r="AI42" s="54"/>
-      <c r="AJ42" s="54"/>
-      <c r="AK42" s="54"/>
-      <c r="AL42" s="54"/>
-      <c r="AM42" s="54"/>
-      <c r="AN42" s="54"/>
-      <c r="AO42" s="54"/>
-      <c r="AP42" s="54"/>
-      <c r="AQ42" s="54"/>
-      <c r="AR42" s="54"/>
-      <c r="AS42" s="54"/>
-      <c r="AT42" s="54"/>
-      <c r="AU42" s="54"/>
-      <c r="AV42" s="54"/>
-      <c r="AW42" s="54"/>
-      <c r="AX42" s="54"/>
-      <c r="AY42" s="54"/>
-      <c r="AZ42" s="54"/>
-    </row>
-    <row r="43" spans="1:52" ht="3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
-      <c r="AA43" s="29"/>
-      <c r="AB43" s="29"/>
-      <c r="AC43" s="29"/>
-      <c r="AD43" s="29"/>
-      <c r="AE43" s="54"/>
-      <c r="AF43" s="54"/>
-      <c r="AG43" s="54"/>
-      <c r="AH43" s="54"/>
-      <c r="AI43" s="54"/>
-      <c r="AJ43" s="54"/>
-      <c r="AK43" s="54"/>
-      <c r="AL43" s="54"/>
-      <c r="AM43" s="54"/>
-      <c r="AN43" s="54"/>
-      <c r="AO43" s="54"/>
-      <c r="AP43" s="54"/>
-      <c r="AQ43" s="54"/>
-      <c r="AR43" s="54"/>
-      <c r="AS43" s="54"/>
-      <c r="AT43" s="54"/>
-      <c r="AU43" s="54"/>
-      <c r="AV43" s="54"/>
-      <c r="AW43" s="54"/>
-      <c r="AX43" s="54"/>
-      <c r="AY43" s="54"/>
-      <c r="AZ43" s="54"/>
-    </row>
-    <row r="44" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="35"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
-      <c r="L44" s="35"/>
-      <c r="M44" s="35"/>
-      <c r="N44" s="35"/>
-      <c r="O44" s="35"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="35"/>
-      <c r="R44" s="35"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="35"/>
-      <c r="U44" s="35"/>
-      <c r="V44" s="35"/>
-      <c r="W44" s="35"/>
-      <c r="X44" s="35"/>
-      <c r="Y44" s="35"/>
-      <c r="Z44" s="35"/>
-      <c r="AA44" s="35"/>
-      <c r="AB44" s="35"/>
-      <c r="AC44" s="35"/>
-      <c r="AD44" s="35"/>
-      <c r="AE44" s="29"/>
-      <c r="AF44" s="29"/>
-      <c r="AG44" s="29"/>
-      <c r="AH44" s="29"/>
-      <c r="AI44" s="29"/>
-      <c r="AJ44" s="29"/>
-      <c r="AK44" s="29"/>
-      <c r="AL44" s="29"/>
-      <c r="AM44" s="29"/>
-      <c r="AN44" s="29"/>
-      <c r="AO44" s="29"/>
-      <c r="AP44" s="29"/>
-      <c r="AQ44" s="29"/>
-      <c r="AR44" s="29"/>
-      <c r="AS44" s="29"/>
-      <c r="AT44" s="29"/>
-      <c r="AU44" s="29"/>
-      <c r="AV44" s="29"/>
-      <c r="AW44" s="29"/>
-      <c r="AX44" s="29"/>
-      <c r="AY44" s="29"/>
-      <c r="AZ44" s="29"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="36"/>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+      <c r="U44" s="36"/>
+      <c r="V44" s="36"/>
+      <c r="W44" s="36"/>
+      <c r="X44" s="36"/>
+      <c r="Y44" s="36"/>
+      <c r="Z44" s="36"/>
+      <c r="AA44" s="36"/>
+      <c r="AB44" s="36"/>
+      <c r="AC44" s="36"/>
+      <c r="AD44" s="36"/>
+      <c r="AE44" s="30"/>
+      <c r="AF44" s="30"/>
+      <c r="AG44" s="30"/>
+      <c r="AH44" s="30"/>
+      <c r="AI44" s="30"/>
+      <c r="AJ44" s="30"/>
+      <c r="AK44" s="30"/>
+      <c r="AL44" s="30"/>
+      <c r="AM44" s="30"/>
+      <c r="AN44" s="30"/>
+      <c r="AO44" s="30"/>
+      <c r="AP44" s="30"/>
+      <c r="AQ44" s="30"/>
+      <c r="AR44" s="30"/>
+      <c r="AS44" s="30"/>
+      <c r="AT44" s="30"/>
+      <c r="AU44" s="30"/>
+      <c r="AV44" s="30"/>
+      <c r="AW44" s="30"/>
+      <c r="AX44" s="30"/>
+      <c r="AY44" s="30"/>
+      <c r="AZ44" s="30"/>
     </row>
     <row r="45" spans="1:52" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" s="34"/>
       <c r="C45" s="34"/>
@@ -2844,240 +2840,240 @@
       <c r="AB45" s="34"/>
       <c r="AC45" s="34"/>
       <c r="AD45" s="34"/>
-      <c r="AE45" s="29"/>
-      <c r="AF45" s="29"/>
-      <c r="AG45" s="29"/>
-      <c r="AH45" s="29"/>
-      <c r="AI45" s="29"/>
-      <c r="AJ45" s="29"/>
-      <c r="AK45" s="29"/>
-      <c r="AL45" s="29"/>
-      <c r="AM45" s="29"/>
-      <c r="AN45" s="29"/>
-      <c r="AO45" s="29"/>
-      <c r="AP45" s="29"/>
-      <c r="AQ45" s="29"/>
-      <c r="AR45" s="29"/>
-      <c r="AS45" s="29"/>
-      <c r="AT45" s="29"/>
-      <c r="AU45" s="29"/>
-      <c r="AV45" s="29"/>
-      <c r="AW45" s="29"/>
-      <c r="AX45" s="29"/>
-      <c r="AY45" s="29"/>
-      <c r="AZ45" s="29"/>
+      <c r="AE45" s="30"/>
+      <c r="AF45" s="30"/>
+      <c r="AG45" s="30"/>
+      <c r="AH45" s="30"/>
+      <c r="AI45" s="30"/>
+      <c r="AJ45" s="30"/>
+      <c r="AK45" s="30"/>
+      <c r="AL45" s="30"/>
+      <c r="AM45" s="30"/>
+      <c r="AN45" s="30"/>
+      <c r="AO45" s="30"/>
+      <c r="AP45" s="30"/>
+      <c r="AQ45" s="30"/>
+      <c r="AR45" s="30"/>
+      <c r="AS45" s="30"/>
+      <c r="AT45" s="30"/>
+      <c r="AU45" s="30"/>
+      <c r="AV45" s="30"/>
+      <c r="AW45" s="30"/>
+      <c r="AX45" s="30"/>
+      <c r="AY45" s="30"/>
+      <c r="AZ45" s="30"/>
     </row>
     <row r="46" spans="1:52" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="31"/>
-      <c r="N46" s="31"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="31"/>
-      <c r="Q46" s="31"/>
-      <c r="R46" s="31"/>
-      <c r="S46" s="31"/>
-      <c r="T46" s="31"/>
-      <c r="U46" s="31"/>
-      <c r="V46" s="31"/>
-      <c r="W46" s="31"/>
-      <c r="X46" s="31"/>
-      <c r="Y46" s="31"/>
-      <c r="Z46" s="31"/>
-      <c r="AA46" s="31"/>
-      <c r="AB46" s="31"/>
-      <c r="AC46" s="31"/>
-      <c r="AD46" s="31"/>
-      <c r="AE46" s="29"/>
-      <c r="AF46" s="29"/>
-      <c r="AG46" s="29"/>
-      <c r="AH46" s="29"/>
-      <c r="AI46" s="29"/>
-      <c r="AJ46" s="29"/>
-      <c r="AK46" s="29"/>
-      <c r="AL46" s="29"/>
-      <c r="AM46" s="29"/>
-      <c r="AN46" s="29"/>
-      <c r="AO46" s="29"/>
-      <c r="AP46" s="29"/>
-      <c r="AQ46" s="29"/>
-      <c r="AR46" s="29"/>
-      <c r="AS46" s="29"/>
-      <c r="AT46" s="29"/>
-      <c r="AU46" s="29"/>
-      <c r="AV46" s="29"/>
-      <c r="AW46" s="29"/>
-      <c r="AX46" s="29"/>
-      <c r="AY46" s="29"/>
-      <c r="AZ46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+      <c r="X46" s="29"/>
+      <c r="Y46" s="29"/>
+      <c r="Z46" s="29"/>
+      <c r="AA46" s="29"/>
+      <c r="AB46" s="29"/>
+      <c r="AC46" s="29"/>
+      <c r="AD46" s="29"/>
+      <c r="AE46" s="30"/>
+      <c r="AF46" s="30"/>
+      <c r="AG46" s="30"/>
+      <c r="AH46" s="30"/>
+      <c r="AI46" s="30"/>
+      <c r="AJ46" s="30"/>
+      <c r="AK46" s="30"/>
+      <c r="AL46" s="30"/>
+      <c r="AM46" s="30"/>
+      <c r="AN46" s="30"/>
+      <c r="AO46" s="30"/>
+      <c r="AP46" s="30"/>
+      <c r="AQ46" s="30"/>
+      <c r="AR46" s="30"/>
+      <c r="AS46" s="30"/>
+      <c r="AT46" s="30"/>
+      <c r="AU46" s="30"/>
+      <c r="AV46" s="30"/>
+      <c r="AW46" s="30"/>
+      <c r="AX46" s="30"/>
+      <c r="AY46" s="30"/>
+      <c r="AZ46" s="30"/>
     </row>
     <row r="47" spans="1:52" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:52" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N48" s="8"/>
       <c r="O48" s="8"/>
-      <c r="P48" s="47"/>
-      <c r="Q48" s="47"/>
-      <c r="R48" s="47"/>
-      <c r="S48" s="47"/>
-      <c r="T48" s="47"/>
-      <c r="U48" s="47"/>
-      <c r="V48" s="47"/>
+      <c r="P48" s="41"/>
+      <c r="Q48" s="41"/>
+      <c r="R48" s="41"/>
+      <c r="S48" s="41"/>
+      <c r="T48" s="41"/>
+      <c r="U48" s="41"/>
+      <c r="V48" s="41"/>
       <c r="W48" s="18"/>
-      <c r="X48" s="47"/>
-      <c r="Y48" s="47"/>
-      <c r="Z48" s="47"/>
-      <c r="AA48" s="47"/>
-      <c r="AB48" s="47"/>
-      <c r="AC48" s="47"/>
-      <c r="AD48" s="47"/>
-      <c r="AE48" s="47"/>
-      <c r="AF48" s="47"/>
+      <c r="X48" s="41"/>
+      <c r="Y48" s="41"/>
+      <c r="Z48" s="41"/>
+      <c r="AA48" s="41"/>
+      <c r="AB48" s="41"/>
+      <c r="AC48" s="41"/>
+      <c r="AD48" s="41"/>
+      <c r="AE48" s="41"/>
+      <c r="AF48" s="41"/>
       <c r="AG48" s="18"/>
-      <c r="AH48" s="47"/>
-      <c r="AI48" s="47"/>
-      <c r="AJ48" s="47"/>
-      <c r="AK48" s="47"/>
-      <c r="AL48" s="47"/>
-      <c r="AM48" s="47"/>
-      <c r="AN48" s="47"/>
-      <c r="AO48" s="47"/>
-      <c r="AP48" s="47"/>
-      <c r="AQ48" s="47"/>
-      <c r="AR48" s="47"/>
-      <c r="AS48" s="47"/>
-      <c r="AT48" s="47"/>
-      <c r="AU48" s="47"/>
-      <c r="AV48" s="47"/>
-      <c r="AW48" s="47"/>
-      <c r="AX48" s="47"/>
-      <c r="AY48" s="47"/>
-      <c r="AZ48" s="47"/>
+      <c r="AH48" s="41"/>
+      <c r="AI48" s="41"/>
+      <c r="AJ48" s="41"/>
+      <c r="AK48" s="41"/>
+      <c r="AL48" s="41"/>
+      <c r="AM48" s="41"/>
+      <c r="AN48" s="41"/>
+      <c r="AO48" s="41"/>
+      <c r="AP48" s="41"/>
+      <c r="AQ48" s="41"/>
+      <c r="AR48" s="41"/>
+      <c r="AS48" s="41"/>
+      <c r="AT48" s="41"/>
+      <c r="AU48" s="41"/>
+      <c r="AV48" s="41"/>
+      <c r="AW48" s="41"/>
+      <c r="AX48" s="41"/>
+      <c r="AY48" s="41"/>
+      <c r="AZ48" s="41"/>
     </row>
     <row r="49" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="P49" s="30" t="s">
+      <c r="P49" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="11"/>
+      <c r="X49" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="11"/>
-      <c r="X49" s="30" t="s">
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="28"/>
+      <c r="AA49" s="28"/>
+      <c r="AB49" s="28"/>
+      <c r="AC49" s="28"/>
+      <c r="AD49" s="28"/>
+      <c r="AE49" s="28"/>
+      <c r="AF49" s="28"/>
+      <c r="AG49" s="11"/>
+      <c r="AH49" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AA49" s="30"/>
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
-      <c r="AE49" s="30"/>
-      <c r="AF49" s="30"/>
-      <c r="AG49" s="11"/>
-      <c r="AH49" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI49" s="30"/>
-      <c r="AJ49" s="30"/>
-      <c r="AK49" s="30"/>
-      <c r="AL49" s="30"/>
-      <c r="AM49" s="30"/>
-      <c r="AN49" s="30"/>
-      <c r="AO49" s="30"/>
-      <c r="AP49" s="30"/>
-      <c r="AQ49" s="30"/>
-      <c r="AR49" s="30"/>
-      <c r="AS49" s="30"/>
-      <c r="AT49" s="30"/>
-      <c r="AU49" s="30"/>
-      <c r="AV49" s="30"/>
-      <c r="AW49" s="30"/>
-      <c r="AX49" s="30"/>
-      <c r="AY49" s="30"/>
-      <c r="AZ49" s="30"/>
+      <c r="AI49" s="28"/>
+      <c r="AJ49" s="28"/>
+      <c r="AK49" s="28"/>
+      <c r="AL49" s="28"/>
+      <c r="AM49" s="28"/>
+      <c r="AN49" s="28"/>
+      <c r="AO49" s="28"/>
+      <c r="AP49" s="28"/>
+      <c r="AQ49" s="28"/>
+      <c r="AR49" s="28"/>
+      <c r="AS49" s="28"/>
+      <c r="AT49" s="28"/>
+      <c r="AU49" s="28"/>
+      <c r="AV49" s="28"/>
+      <c r="AW49" s="28"/>
+      <c r="AX49" s="28"/>
+      <c r="AY49" s="28"/>
+      <c r="AZ49" s="28"/>
     </row>
     <row r="50" spans="1:52" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F50" s="8"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
-      <c r="I50" s="47"/>
-      <c r="J50" s="47"/>
-      <c r="K50" s="47"/>
-      <c r="L50" s="47"/>
-      <c r="M50" s="47"/>
-      <c r="N50" s="47"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="41"/>
+      <c r="K50" s="41"/>
+      <c r="L50" s="41"/>
+      <c r="M50" s="41"/>
+      <c r="N50" s="41"/>
       <c r="O50" s="18"/>
-      <c r="P50" s="47"/>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47"/>
-      <c r="S50" s="47"/>
-      <c r="T50" s="47"/>
-      <c r="U50" s="47"/>
-      <c r="V50" s="47"/>
-      <c r="W50" s="47"/>
-      <c r="X50" s="47"/>
-      <c r="Y50" s="47"/>
-      <c r="Z50" s="47"/>
-      <c r="AA50" s="47"/>
-      <c r="AB50" s="47"/>
-      <c r="AC50" s="47"/>
-      <c r="AD50" s="47"/>
-      <c r="AE50" s="47"/>
-      <c r="AF50" s="47"/>
+      <c r="P50" s="41"/>
+      <c r="Q50" s="41"/>
+      <c r="R50" s="41"/>
+      <c r="S50" s="41"/>
+      <c r="T50" s="41"/>
+      <c r="U50" s="41"/>
+      <c r="V50" s="41"/>
+      <c r="W50" s="41"/>
+      <c r="X50" s="41"/>
+      <c r="Y50" s="41"/>
+      <c r="Z50" s="41"/>
+      <c r="AA50" s="41"/>
+      <c r="AB50" s="41"/>
+      <c r="AC50" s="41"/>
+      <c r="AD50" s="41"/>
+      <c r="AE50" s="41"/>
+      <c r="AF50" s="41"/>
       <c r="AG50" s="8"/>
       <c r="AH50" s="8"/>
     </row>
     <row r="51" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="G51" s="30" t="s">
+      <c r="G51" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
-      <c r="L51" s="30"/>
-      <c r="M51" s="30"/>
-      <c r="N51" s="30"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q51" s="30"/>
-      <c r="R51" s="30"/>
-      <c r="S51" s="30"/>
-      <c r="T51" s="30"/>
-      <c r="U51" s="30"/>
-      <c r="V51" s="30"/>
-      <c r="W51" s="30"/>
-      <c r="X51" s="30"/>
-      <c r="Y51" s="30"/>
-      <c r="Z51" s="30"/>
-      <c r="AA51" s="30"/>
-      <c r="AB51" s="30"/>
-      <c r="AC51" s="30"/>
-      <c r="AD51" s="30"/>
-      <c r="AE51" s="30"/>
-      <c r="AF51" s="30"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="28"/>
+      <c r="S51" s="28"/>
+      <c r="T51" s="28"/>
+      <c r="U51" s="28"/>
+      <c r="V51" s="28"/>
+      <c r="W51" s="28"/>
+      <c r="X51" s="28"/>
+      <c r="Y51" s="28"/>
+      <c r="Z51" s="28"/>
+      <c r="AA51" s="28"/>
+      <c r="AB51" s="28"/>
+      <c r="AC51" s="28"/>
+      <c r="AD51" s="28"/>
+      <c r="AE51" s="28"/>
+      <c r="AF51" s="28"/>
       <c r="AG51" s="9"/>
       <c r="AH51" s="9"/>
     </row>
@@ -3100,6 +3096,13 @@
     <mergeCell ref="A17:Q17"/>
     <mergeCell ref="W24:AC24"/>
     <mergeCell ref="S19:V23"/>
+    <mergeCell ref="Q16:V16"/>
+    <mergeCell ref="AG15:AJ15"/>
+    <mergeCell ref="AS16:AZ16"/>
+    <mergeCell ref="AL16:AQ16"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:R26"/>
     <mergeCell ref="AQ4:AZ4"/>
     <mergeCell ref="AQ5:AZ5"/>
     <mergeCell ref="AQ6:AZ6"/>
@@ -3124,15 +3127,6 @@
     <mergeCell ref="W16:AB16"/>
     <mergeCell ref="AG16:AJ16"/>
     <mergeCell ref="Q14:V15"/>
-    <mergeCell ref="Q16:V16"/>
-    <mergeCell ref="AG15:AJ15"/>
-    <mergeCell ref="AS16:AZ16"/>
-    <mergeCell ref="AL16:AQ16"/>
-    <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:R26"/>
-    <mergeCell ref="S26:V26"/>
-    <mergeCell ref="W26:AC26"/>
     <mergeCell ref="AS19:AZ23"/>
     <mergeCell ref="AK19:AR23"/>
     <mergeCell ref="AD19:AJ23"/>
@@ -3142,8 +3136,6 @@
     <mergeCell ref="AD26:AJ26"/>
     <mergeCell ref="AK26:AR26"/>
     <mergeCell ref="AS26:AZ26"/>
-    <mergeCell ref="S25:V25"/>
-    <mergeCell ref="W25:AC25"/>
     <mergeCell ref="AD25:AJ25"/>
     <mergeCell ref="AK25:AR25"/>
     <mergeCell ref="AS25:AZ25"/>
@@ -3156,6 +3148,15 @@
     <mergeCell ref="AK27:AR27"/>
     <mergeCell ref="S27:V27"/>
     <mergeCell ref="W27:AC27"/>
+    <mergeCell ref="S26:V26"/>
+    <mergeCell ref="W26:AC26"/>
+    <mergeCell ref="S25:V25"/>
+    <mergeCell ref="W25:AC25"/>
+    <mergeCell ref="AS30:AZ30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:R29"/>
+    <mergeCell ref="S29:V29"/>
+    <mergeCell ref="W29:AC29"/>
     <mergeCell ref="AD29:AJ29"/>
     <mergeCell ref="AK29:AR29"/>
     <mergeCell ref="AS29:AZ29"/>
@@ -3169,27 +3170,16 @@
     <mergeCell ref="AS28:AZ28"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="E27:R27"/>
+    <mergeCell ref="AD31:AJ31"/>
+    <mergeCell ref="AK31:AR31"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:R31"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="E30:R30"/>
     <mergeCell ref="S30:V30"/>
     <mergeCell ref="W30:AC30"/>
     <mergeCell ref="AD30:AJ30"/>
     <mergeCell ref="AK30:AR30"/>
-    <mergeCell ref="AS30:AZ30"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:R29"/>
-    <mergeCell ref="S29:V29"/>
-    <mergeCell ref="W29:AC29"/>
-    <mergeCell ref="W32:AC32"/>
-    <mergeCell ref="AD32:AJ32"/>
-    <mergeCell ref="AK32:AR32"/>
-    <mergeCell ref="AS32:AZ32"/>
-    <mergeCell ref="S31:V31"/>
-    <mergeCell ref="W31:AC31"/>
-    <mergeCell ref="AD31:AJ31"/>
-    <mergeCell ref="AK31:AR31"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="E31:R31"/>
     <mergeCell ref="AL36:AZ37"/>
     <mergeCell ref="AS31:AZ31"/>
     <mergeCell ref="S32:V32"/>
@@ -3203,6 +3193,17 @@
     <mergeCell ref="AE44:AK44"/>
     <mergeCell ref="AL44:AZ44"/>
     <mergeCell ref="AL41:AZ43"/>
+    <mergeCell ref="A42:B43"/>
+    <mergeCell ref="C42:P43"/>
+    <mergeCell ref="Q42:S43"/>
+    <mergeCell ref="T42:V43"/>
+    <mergeCell ref="W42:AD43"/>
+    <mergeCell ref="W32:AC32"/>
+    <mergeCell ref="AD32:AJ32"/>
+    <mergeCell ref="AK32:AR32"/>
+    <mergeCell ref="AS32:AZ32"/>
+    <mergeCell ref="S31:V31"/>
+    <mergeCell ref="W31:AC31"/>
     <mergeCell ref="G51:N51"/>
     <mergeCell ref="AH49:AZ49"/>
     <mergeCell ref="A46:AD46"/>
@@ -3213,11 +3214,6 @@
     <mergeCell ref="AL46:AZ46"/>
     <mergeCell ref="X49:AF49"/>
     <mergeCell ref="P49:V49"/>
-    <mergeCell ref="A42:B43"/>
-    <mergeCell ref="C42:P43"/>
-    <mergeCell ref="Q42:S43"/>
-    <mergeCell ref="T42:V43"/>
-    <mergeCell ref="W42:AD43"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.59055118110236227" top="0.59055118110236227" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
